--- a/data/1/6.3 fig1 b 10.xlsx
+++ b/data/1/6.3 fig1 b 10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11280"/>
+    <workbookView windowWidth="27945" windowHeight="10740"/>
   </bookViews>
   <sheets>
     <sheet name="6.3 fig1 p 10 43" sheetId="1" r:id="rId1"/>
@@ -1985,13 +1985,13 @@
         <v>8.23</v>
       </c>
       <c r="I18">
-        <v>3.98</v>
+        <v>5.98</v>
       </c>
       <c r="J18">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="L18">
         <v>6.91</v>
@@ -2035,13 +2035,13 @@
         <v>9.08</v>
       </c>
       <c r="I19">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="J19">
-        <v>4.35</v>
+        <v>5.85</v>
       </c>
       <c r="K19">
-        <v>4.28</v>
+        <v>5.88</v>
       </c>
       <c r="L19">
         <v>7.24</v>
@@ -2085,13 +2085,13 @@
         <v>8.74</v>
       </c>
       <c r="I20">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="J20">
-        <v>5.61</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>5.7</v>
+        <v>6.38</v>
       </c>
       <c r="L20">
         <v>6.8</v>
@@ -2282,16 +2282,16 @@
         <v>8.03</v>
       </c>
       <c r="I25">
-        <v>5.16</v>
+        <v>5.66</v>
       </c>
       <c r="J25">
-        <v>4.96</v>
+        <v>5.96</v>
       </c>
       <c r="K25">
-        <v>4.98</v>
+        <v>5.98</v>
       </c>
       <c r="L25">
-        <v>7.06</v>
+        <v>6.06</v>
       </c>
       <c r="M25">
         <v>7.16</v>
